--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.1-8B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.1-8B-Instruct/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>201</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>418</v>
+        <v>202</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>196</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>406</v>
+        <v>178</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.1-8B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.1-8B-Instruct/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D2">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D3">
-        <v>196</v>
+        <v>166</v>
       </c>
       <c r="E3">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>178</v>
+        <v>230</v>
       </c>
       <c r="H3">
         <v>426</v>
